--- a/dashboard/ui-review/client-timesheet-export.xlsx
+++ b/dashboard/ui-review/client-timesheet-export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>Team timesheet</t>
   </si>
@@ -19,13 +19,13 @@
     <t>Period</t>
   </si>
   <si>
-    <t>2026-10-01 to 2026-10-01</t>
+    <t>2026-10-02 to 2026-10-02</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>10/1/2026, 7:14:34 PM</t>
+    <t>10/2/2026, 4:49:02 PM</t>
   </si>
   <si>
     <t>Records</t>
@@ -37,13 +37,10 @@
     <t>10m</t>
   </si>
   <si>
-    <t>Break</t>
+    <t>Idle</t>
   </si>
   <si>
     <t>0s</t>
-  </si>
-  <si>
-    <t>Idle</t>
   </si>
   <si>
     <t>Employee</t>
@@ -511,17 +508,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +528,6 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -549,7 +545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -568,28 +564,22 @@
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="2" t="s">
+    </row>
+    <row r="6" ht="23" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="23" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
@@ -597,118 +587,103 @@
       <c r="G6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="E10" s="5">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>9</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:H10"/>
+  <autoFilter ref="A6:G10"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
